--- a/New_Outputs/Table3_Regression_SOWS_HT4_HT6.xlsx
+++ b/New_Outputs/Table3_Regression_SOWS_HT4_HT6.xlsx
@@ -12,27 +12,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="74">
   <si>
     <t xml:space="preserve">Predictor</t>
   </si>
   <si>
-    <t xml:space="preserve">Hydrocodone group: ROE + 5-HT4 + 5-HT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydrocodone group: + 5-HT4 x 5-HT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydrocodone group: + Sex, MQS, DOU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tramadol group: ROE + 5-HT4 + 5-HT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tramadol group: + 5-HT4 x 5-HT6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tramadol group: + Sex, MQS, DOU</t>
+    <t xml:space="preserve">Hydrocodone group: M3 ROE + 5-HT4 + 5-HT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrocodone group: M4 + ROE x 5-HT4 + ROE x 5-HT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydrocodone group: M5 + Sex, log MME, MQS non-opioid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tramadol group: M3 ROE + 5-HT4 + 5-HT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tramadol group: M4 + ROE x 5-HT4 + ROE x 5-HT6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tramadol group: M5 + Sex, log MME, MQS non-opioid</t>
   </si>
   <si>
     <t xml:space="preserve">Intercept</t>
@@ -41,19 +41,19 @@
     <t xml:space="preserve">10.553</t>
   </si>
   <si>
-    <t xml:space="preserve">12.584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.410</t>
+    <t xml:space="preserve">-1.482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-21.591</t>
   </si>
   <si>
     <t xml:space="preserve">-11.923</t>
   </si>
   <si>
-    <t xml:space="preserve">-8.269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.530</t>
+    <t xml:space="preserve">19.922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.272</t>
   </si>
   <si>
     <t xml:space="preserve">log10 ROE</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">-1.074</t>
   </si>
   <si>
-    <t xml:space="preserve">0.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.991</t>
+    <t xml:space="preserve">-5.052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.497*</t>
   </si>
   <si>
     <t xml:space="preserve">-5.916</t>
   </si>
   <si>
-    <t xml:space="preserve">-5.307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.336</t>
+    <t xml:space="preserve">1.841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.451</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT4 activity</t>
@@ -83,19 +83,19 @@
     <t xml:space="preserve">6.950</t>
   </si>
   <si>
-    <t xml:space="preserve">11.466*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.913</t>
+    <t xml:space="preserve">-4.924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.222</t>
   </si>
   <si>
     <t xml:space="preserve">-5.830</t>
   </si>
   <si>
-    <t xml:space="preserve">-9.099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7.113</t>
+    <t xml:space="preserve">-109.583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-112.214</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT6 activity</t>
@@ -104,58 +104,79 @@
     <t xml:space="preserve">16.595*</t>
   </si>
   <si>
-    <t xml:space="preserve">19.012**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.573</t>
+    <t xml:space="preserve">-100.061**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-105.067**</t>
   </si>
   <si>
     <t xml:space="preserve">12.737*</t>
   </si>
   <si>
-    <t xml:space="preserve">15.055*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.086*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5-HT4 x 5-HT6</t>
+    <t xml:space="preserve">85.570</t>
+  </si>
+  <si>
+    <t xml:space="preserve">209.565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-HT4 x log10 ROE</t>
   </si>
   <si>
     <t xml:space="preserve">--</t>
   </si>
   <si>
-    <t xml:space="preserve">38.438*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.345</t>
+    <t xml:space="preserve">-4.914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-25.742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-26.028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5-HT6 x log10 ROE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-38.608**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-38.120**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.561</t>
   </si>
   <si>
     <t xml:space="preserve">Sex (female = 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">-7.394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.749</t>
+    <t xml:space="preserve">-1.489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log10 MME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.421</t>
   </si>
   <si>
     <t xml:space="preserve">MQS non-opioid</t>
   </si>
   <si>
-    <t xml:space="preserve">0.081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duration of opioid use (yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.158</t>
+    <t xml:space="preserve">0.257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.170</t>
   </si>
   <si>
     <t xml:space="preserve">n</t>
@@ -164,28 +185,34 @@
     <t xml:space="preserve">19</t>
   </si>
   <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
     <t xml:space="preserve">adj. R2</t>
   </si>
   <si>
     <t xml:space="preserve">0.336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.388</t>
+    <t xml:space="preserve">0.670</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.765</t>
   </si>
   <si>
     <t xml:space="preserve">0.268</t>
   </si>
   <si>
-    <t xml:space="preserve">0.237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176</t>
+    <t xml:space="preserve">0.206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.346</t>
   </si>
   <si>
     <t xml:space="preserve">model p</t>
@@ -194,19 +221,19 @@
     <t xml:space="preserve">0.027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.055</t>
+    <t xml:space="preserve">0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003</t>
   </si>
   <si>
     <t xml:space="preserve">0.072</t>
   </si>
   <si>
-    <t xml:space="preserve">0.125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.251</t>
+    <t xml:space="preserve">0.188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.300</t>
   </si>
 </sst>
 </file>
@@ -671,45 +698,45 @@
       <c r="C6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>36</v>
+      <c r="D6" t="s">
+        <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
+      </c>
+      <c r="G6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>36</v>
+      <c r="C7" t="s">
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>36</v>
+      <c r="F7" t="s">
+        <v>44</v>
       </c>
       <c r="G7" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>36</v>
@@ -718,7 +745,7 @@
         <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>36</v>
@@ -727,12 +754,12 @@
         <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>36</v>
@@ -741,7 +768,7 @@
         <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>36</v>
@@ -750,76 +777,99 @@
         <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" t="s">
-        <v>49</v>
+        <v>52</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" t="s">
-        <v>50</v>
+        <v>53</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>36</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D13" t="s">
+        <v>70</v>
+      </c>
+      <c r="E13" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/New_Outputs/Table3_Regression_SOWS_HT4_HT6.xlsx
+++ b/New_Outputs/Table3_Regression_SOWS_HT4_HT6.xlsx
@@ -38,85 +38,85 @@
     <t xml:space="preserve">Intercept</t>
   </si>
   <si>
-    <t xml:space="preserve">10.553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1.482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-21.591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-11.923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.272</t>
+    <t xml:space="preserve">9.060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-19.214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.743*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.447**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.152</t>
   </si>
   <si>
     <t xml:space="preserve">log10 ROE</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8.497*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.451</t>
+    <t xml:space="preserve">-1.507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.961*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.452*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.696</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT4 activity</t>
   </si>
   <si>
-    <t xml:space="preserve">6.950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-4.924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9.222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-109.583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-112.214</t>
+    <t xml:space="preserve">7.082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.740</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-89.547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-57.889</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT6 activity</t>
   </si>
   <si>
-    <t xml:space="preserve">16.595*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-100.061**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-105.067**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.737*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85.570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">209.565</t>
+    <t xml:space="preserve">12.152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.801*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.021</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT4 x log10 ROE</t>
@@ -125,115 +125,115 @@
     <t xml:space="preserve">--</t>
   </si>
   <si>
-    <t xml:space="preserve">-4.914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5.739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-25.742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-26.028</t>
+    <t xml:space="preserve">-3.783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20.640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-12.681</t>
   </si>
   <si>
     <t xml:space="preserve">5-HT6 x log10 ROE</t>
   </si>
   <si>
-    <t xml:space="preserve">-38.608**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-38.120**</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.561</t>
+    <t xml:space="preserve">5.509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.721*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.987</t>
   </si>
   <si>
     <t xml:space="preserve">Sex (female = 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">-1.489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2.037</t>
+    <t xml:space="preserve">-4.208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.682</t>
   </si>
   <si>
     <t xml:space="preserve">log10 MME</t>
   </si>
   <si>
-    <t xml:space="preserve">4.825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.421</t>
+    <t xml:space="preserve">17.289*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.390</t>
   </si>
   <si>
     <t xml:space="preserve">MQS non-opioid</t>
   </si>
   <si>
-    <t xml:space="preserve">0.257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.170</t>
+    <t xml:space="preserve">0.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.226</t>
   </si>
   <si>
     <t xml:space="preserve">n</t>
   </si>
   <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
   </si>
   <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
     <t xml:space="preserve">adj. R2</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.670</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.346</t>
+    <t xml:space="preserve">0.204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.502</t>
   </si>
   <si>
     <t xml:space="preserve">model p</t>
   </si>
   <si>
-    <t xml:space="preserve">0.027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.300</t>
+    <t xml:space="preserve">0.063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.070</t>
   </si>
 </sst>
 </file>
